--- a/artfynd/A 56447-2025 artfynd.xlsx
+++ b/artfynd/A 56447-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133706228</v>
+        <v>133706296</v>
       </c>
       <c r="B2" t="n">
-        <v>58260</v>
+        <v>4820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>100857</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Robust tickgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dorcatoma robusta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Strand, 1938</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>795710</v>
+        <v>795810</v>
       </c>
       <c r="R2" t="n">
-        <v>7177608</v>
+        <v>7177664</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -776,6 +772,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>död björk m fnöskticka</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -788,6 +789,229 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133706228</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Harrsjön NR, centrala lövskogarna, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>795710</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7177608</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133706225</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Harrsjön NR, centrala lövskogarna, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>795709</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7177608</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56447-2025 artfynd.xlsx
+++ b/artfynd/A 56447-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,8 +1027,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133706225</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>